--- a/ECB_mean_lt.xlsx
+++ b/ECB_mean_lt.xlsx
@@ -69,7 +69,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -274,7 +274,7 @@
         <v>44378</v>
       </c>
       <c r="B20" s="2">
-        <v>3.7110083240476386</v>
+        <v>3.711008324047639</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -362,7 +362,7 @@
         <v>44621</v>
       </c>
       <c r="B28" s="2">
-        <v>3.8507329289080485</v>
+        <v>3.850732928908049</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -549,7 +549,7 @@
         <v>45139</v>
       </c>
       <c r="B45" s="2">
-        <v>3.9115942924127545</v>
+        <v>3.9115942924127554</v>
       </c>
       <c r="C45" s="2">
         <v>3</v>
@@ -615,7 +615,7 @@
         <v>45323</v>
       </c>
       <c r="B51" s="2">
-        <v>4.3105899595757666</v>
+        <v>4.3105899595757675</v>
       </c>
       <c r="C51" s="2">
         <v>3</v>
@@ -648,7 +648,7 @@
         <v>45413</v>
       </c>
       <c r="B54" s="2">
-        <v>4.1531256199256514</v>
+        <v>4.1531256199256497</v>
       </c>
       <c r="C54" s="2">
         <v>3.0999999046325684</v>
@@ -747,7 +747,7 @@
         <v>45689</v>
       </c>
       <c r="B63" s="2">
-        <v>4.7441090386901781</v>
+        <v>4.7441090386901772</v>
       </c>
       <c r="C63" s="2">
         <v>4</v>
@@ -768,8 +768,107 @@
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="B65" s="2">
+        <v>5.0562619123757493</v>
+      </c>
+      <c r="C65" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B66" s="2">
+        <v>4.608412512839303</v>
+      </c>
+      <c r="C66" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B67" s="2">
+        <v>4.5640929296540538</v>
+      </c>
+      <c r="C67" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B68" s="2">
+        <v>4.5685024409211845</v>
+      </c>
+      <c r="C68" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B69" s="2">
+        <v>4.6031118205682739</v>
+      </c>
+      <c r="C69" s="2">
+        <v>3.0999999046325684</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B70" s="2">
+        <v>4.4520059293155159</v>
+      </c>
+      <c r="C70" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B71" s="2">
+        <v>4.5329328789571166</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B72" s="2">
+        <v>4.5882229036801636</v>
+      </c>
+      <c r="C72" s="2">
+        <v>3.4000000953674316</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B73" s="2">
+        <v>4.5141543967414774</v>
+      </c>
+      <c r="C73" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
     </row>
   </sheetData>
 </worksheet>
